--- a/Revenue Report/archive/Revenue_Report_July_2026_H1.xlsx
+++ b/Revenue Report/archive/Revenue_Report_July_2026_H1.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="103">
   <si>
     <t>Period</t>
   </si>
@@ -296,16 +296,10 @@
     <t>July 2026 H1  (2026-07-01 to 2026-07-14 inclusive)</t>
   </si>
   <si>
-    <t>Run date (UTC)</t>
-  </si>
-  <si>
-    <t>2026-07-16</t>
-  </si>
-  <si>
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 07:14:53</t>
+    <t>2026-07-16 10:03:14</t>
   </si>
   <si>
     <t>Source</t>
@@ -1223,7 +1217,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="18.45703125" customWidth="true" bestFit="true"/>
@@ -1280,34 +1274,26 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="1">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>102</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s" s="0">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="1">
-        <v>6</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="0">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="1">
-        <v>103</v>
-      </c>
-      <c r="B10" t="s" s="0">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/Revenue Report/archive/Revenue_Report_July_2026_H1.xlsx
+++ b/Revenue Report/archive/Revenue_Report_July_2026_H1.xlsx
@@ -299,7 +299,7 @@
     <t>Generated (UTC)</t>
   </si>
   <si>
-    <t>2026-07-16 10:03:14</t>
+    <t>2026-07-16 15:22:47</t>
   </si>
   <si>
     <t>Source</t>
